--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9020,0.0128,0.0243,0.0349</t>
-  </si>
-  <si>
-    <t>0.0192,0.0200,0.0007,0.9877</t>
-  </si>
-  <si>
-    <t>0.6456,0.0045,0.0019,0.4803</t>
-  </si>
-  <si>
-    <t>0.0400,0.0038,0.0013,0.9825</t>
-  </si>
-  <si>
-    <t>0.9941,0.0010,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9908,0.0013,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.9922,0.0014,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9970,0.0005,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9925,0.0013,0.0001,0.0024</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9884,0.0014,0.0001,0.0047</t>
-  </si>
-  <si>
-    <t>0.7386,0.0555,0.2288,0.0092</t>
-  </si>
-  <si>
-    <t>0.0624,0.0255,0.9480,0.0032</t>
-  </si>
-  <si>
-    <t>0.1886,0.0269,0.8840,0.0009</t>
-  </si>
-  <si>
-    <t>0.0699,0.0210,0.9166,0.0042</t>
-  </si>
-  <si>
-    <t>0.6530,0.0095,0.4048,0.0267</t>
-  </si>
-  <si>
-    <t>0.1351,0.8650,0.0387,0.0032</t>
-  </si>
-  <si>
-    <t>0.0682,0.9313,0.0128,0.0015</t>
-  </si>
-  <si>
-    <t>0.1540,0.8735,0.0234,0.0023</t>
-  </si>
-  <si>
-    <t>0.1145,0.9179,0.0054,0.0010</t>
-  </si>
-  <si>
-    <t>0.0267,0.9709,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.7089,0.0181,0.4392,0.0020</t>
-  </si>
-  <si>
-    <t>0.4512,0.0281,0.6016,0.0084</t>
-  </si>
-  <si>
-    <t>0.1238,0.0035,0.9518,0.0008</t>
-  </si>
-  <si>
-    <t>0.0610,0.0124,0.9231,0.0138</t>
-  </si>
-  <si>
-    <t>0.1236,0.0084,0.9164,0.0054</t>
-  </si>
-  <si>
-    <t>0.4627,0.0021,0.7234,0.0054</t>
-  </si>
-  <si>
-    <t>0.0234,0.0035,0.9807,0.0048</t>
-  </si>
-  <si>
-    <t>0.6125,0.4513,0.0335,0.0058</t>
-  </si>
-  <si>
-    <t>0.6812,0.1511,0.2524,0.0074</t>
-  </si>
-  <si>
-    <t>0.0034,0.0121,0.9849,0.0157</t>
-  </si>
-  <si>
-    <t>0.0216,0.8277,0.3588,0.0004</t>
-  </si>
-  <si>
-    <t>0.8391,0.1150,0.0381,0.0196</t>
-  </si>
-  <si>
-    <t>0.8587,0.0616,0.0909,0.0044</t>
-  </si>
-  <si>
-    <t>0.7897,0.2808,0.0145,0.0019</t>
-  </si>
-  <si>
-    <t>0.1085,0.8345,0.2201,0.0078</t>
-  </si>
-  <si>
-    <t>0.0421,0.7491,0.5967,0.0052</t>
-  </si>
-  <si>
-    <t>0.0835,0.0257,0.8703,0.0351</t>
-  </si>
-  <si>
-    <t>0.0309,0.0241,0.7154,0.3350</t>
-  </si>
-  <si>
-    <t>0.1817,0.0123,0.8667,0.0046</t>
-  </si>
-  <si>
-    <t>0.0290,0.1898,0.9368,0.0010</t>
-  </si>
-  <si>
-    <t>0.0073,0.9715,0.0325,0.0011</t>
-  </si>
-  <si>
-    <t>0.0074,0.0027,0.9750,0.0173</t>
-  </si>
-  <si>
-    <t>0.0307,0.7921,0.0389,0.7263</t>
-  </si>
-  <si>
-    <t>0.0021,0.9845,0.0210,0.0380</t>
-  </si>
-  <si>
-    <t>0.0265,0.9375,0.1544,0.0031</t>
-  </si>
-  <si>
-    <t>0.0017,0.9922,0.0074,0.0055</t>
-  </si>
-  <si>
-    <t>0.0109,0.0450,0.9630,0.0033</t>
-  </si>
-  <si>
-    <t>0.0051,0.2910,0.9656,0.0029</t>
-  </si>
-  <si>
-    <t>0.4579,0.0095,0.7589,0.0022</t>
-  </si>
-  <si>
-    <t>0.0190,0.0023,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.0032,0.9813,0.0169</t>
-  </si>
-  <si>
-    <t>0.0248,0.0119,0.9693,0.0018</t>
-  </si>
-  <si>
-    <t>0.9862,0.0159,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9891,0.0025,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9691,0.0205,0.0049,0.0018</t>
-  </si>
-  <si>
-    <t>0.0144,0.0204,0.9832,0.0030</t>
-  </si>
-  <si>
-    <t>0.9845,0.0039,0.0001,0.0032</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9910,0.0027,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.0033,0.9301,0.7855,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.0113,0.9794,0.0074</t>
-  </si>
-  <si>
-    <t>0.0131,0.0019,0.9826,0.0045</t>
-  </si>
-  <si>
-    <t>0.0033,0.9499,0.6040,0.0011</t>
-  </si>
-  <si>
-    <t>0.0006,0.0035,0.9959,0.0016</t>
-  </si>
-  <si>
-    <t>0.0791,0.8510,0.0948,0.0011</t>
-  </si>
-  <si>
-    <t>0.0206,0.9692,0.0195,0.0003</t>
-  </si>
-  <si>
-    <t>0.8324,0.0304,0.2084,0.0099</t>
-  </si>
-  <si>
-    <t>0.8594,0.0601,0.1109,0.0083</t>
-  </si>
-  <si>
-    <t>0.0262,0.0166,0.9666,0.0029</t>
-  </si>
-  <si>
-    <t>0.0176,0.8489,0.6893,0.0066</t>
-  </si>
-  <si>
-    <t>0.0021,0.7493,0.9587,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.9732,0.6262,0.0018</t>
-  </si>
-  <si>
-    <t>0.0028,0.9522,0.6326,0.0004</t>
-  </si>
-  <si>
-    <t>0.0133,0.0005,0.0083,0.9772</t>
-  </si>
-  <si>
-    <t>0.0177,0.0036,0.0009,0.9893</t>
-  </si>
-  <si>
-    <t>0.0091,0.0009,0.0001,0.9964</t>
-  </si>
-  <si>
-    <t>0.0565,0.0023,0.0027,0.9742</t>
-  </si>
-  <si>
-    <t>0.0715,0.0026,0.0029,0.9669</t>
-  </si>
-  <si>
-    <t>0.0085,0.0004,0.0016,0.9935</t>
-  </si>
-  <si>
-    <t>0.0003,0.9912,0.7726,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.7899,0.9659,0.0006</t>
-  </si>
-  <si>
-    <t>0.0081,0.1790,0.8761,0.0190</t>
-  </si>
-  <si>
-    <t>0.0026,0.8196,0.9316,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.9690,0.6580,0.0001</t>
-  </si>
-  <si>
-    <t>0.0177,0.7377,0.7448,0.0026</t>
-  </si>
-  <si>
-    <t>0.9917,0.0030,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9872,0.0035,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9893,0.0072,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9903,0.0025,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.9811,0.0113,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9949,0.0020,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9818,0.0014,0.0000,0.0074</t>
-  </si>
-  <si>
-    <t>0.9847,0.0110,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9941,0.0002,0.0000,0.0034</t>
-  </si>
-  <si>
-    <t>0.9945,0.0007,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9827,0.0025,0.0003,0.0065</t>
-  </si>
-  <si>
-    <t>0.9943,0.0013,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9915,0.0026,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9940,0.0003,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.9927,0.0012,0.0001,0.0024</t>
-  </si>
-  <si>
-    <t>0.0014,0.0020,0.9936,0.0059</t>
-  </si>
-  <si>
-    <t>0.1263,0.0544,0.8650,0.0028</t>
-  </si>
-  <si>
-    <t>0.7980,0.0080,0.1572,0.0289</t>
-  </si>
-  <si>
-    <t>0.0123,0.0103,0.9849,0.0013</t>
-  </si>
-  <si>
-    <t>0.0309,0.9703,0.0023,0.0013</t>
-  </si>
-  <si>
-    <t>0.1118,0.9046,0.0186,0.0019</t>
-  </si>
-  <si>
-    <t>0.3749,0.7437,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.5708,0.5104,0.0183,0.0105</t>
-  </si>
-  <si>
-    <t>0.3030,0.8093,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.0164,0.9779,0.0028,0.0020</t>
-  </si>
-  <si>
-    <t>0.9746,0.0308,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.7731,0.0391,0.2310,0.0226</t>
-  </si>
-  <si>
-    <t>0.4641,0.0153,0.6541,0.0133</t>
-  </si>
-  <si>
-    <t>0.5706,0.0939,0.4087,0.0365</t>
-  </si>
-  <si>
-    <t>0.6161,0.1256,0.2751,0.0161</t>
-  </si>
-  <si>
-    <t>0.0385,0.0020,0.0202,0.9609</t>
-  </si>
-  <si>
-    <t>0.0079,0.9763,0.0369,0.0083</t>
-  </si>
-  <si>
-    <t>0.0007,0.9858,0.2022,0.0199</t>
-  </si>
-  <si>
-    <t>0.0496,0.9437,0.0090,0.0037</t>
-  </si>
-  <si>
-    <t>0.0037,0.9905,0.0192,0.0007</t>
-  </si>
-  <si>
-    <t>0.0844,0.8904,0.0847,0.0021</t>
-  </si>
-  <si>
-    <t>0.8873,0.0990,0.0428,0.0056</t>
-  </si>
-  <si>
-    <t>0.9046,0.1403,0.0049,0.0022</t>
-  </si>
-  <si>
-    <t>0.9904,0.0034,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9911,0.0018,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9879,0.0008,0.0001,0.0064</t>
-  </si>
-  <si>
-    <t>0.9723,0.0056,0.0031,0.0085</t>
-  </si>
-  <si>
-    <t>0.9914,0.0010,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.9298,0.0445,0.0199,0.0152</t>
-  </si>
-  <si>
-    <t>0.9904,0.0004,0.0001,0.0068</t>
-  </si>
-  <si>
-    <t>0.9915,0.0019,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.0021,0.6610,0.9707,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.6264,0.9548,0.0005</t>
-  </si>
-  <si>
-    <t>0.0121,0.1431,0.9539,0.0026</t>
-  </si>
-  <si>
-    <t>0.0332,0.0888,0.9122,0.0023</t>
-  </si>
-  <si>
-    <t>0.7328,0.1030,0.0866,0.0836</t>
-  </si>
-  <si>
-    <t>0.9146,0.0100,0.0800,0.0019</t>
-  </si>
-  <si>
-    <t>0.3945,0.0028,0.6230,0.0336</t>
-  </si>
-  <si>
-    <t>0.5716,0.0732,0.3957,0.0093</t>
-  </si>
-  <si>
-    <t>0.0249,0.0005,0.0009,0.9898</t>
-  </si>
-  <si>
-    <t>0.0008,0.0028,0.0003,0.9988</t>
-  </si>
-  <si>
-    <t>0.0068,0.0025,0.0230,0.9775</t>
-  </si>
-  <si>
-    <t>0.0034,0.0003,0.0003,0.9984</t>
-  </si>
-  <si>
-    <t>0.0021,0.9572,0.5838,0.0005</t>
-  </si>
-  <si>
-    <t>0.9596,0.0086,0.0006,0.0131</t>
-  </si>
-  <si>
-    <t>0.1702,0.8387,0.0064,0.0187</t>
-  </si>
-  <si>
-    <t>0.9658,0.0137,0.0018,0.0066</t>
-  </si>
-  <si>
-    <t>0.8972,0.1682,0.0049,0.0026</t>
-  </si>
-  <si>
-    <t>0.9366,0.0071,0.0054,0.0340</t>
-  </si>
-  <si>
-    <t>0.2657,0.0044,0.0177,0.8292</t>
-  </si>
-  <si>
-    <t>0.9634,0.0377,0.0034,0.0022</t>
-  </si>
-  <si>
-    <t>0.0522,0.0911,0.7810,0.2168</t>
-  </si>
-  <si>
-    <t>0.9012,0.0021,0.0041,0.0874</t>
-  </si>
-  <si>
-    <t>0.9505,0.0015,0.0024,0.0364</t>
-  </si>
-  <si>
-    <t>0.7716,0.1640,0.0171,0.0477</t>
-  </si>
-  <si>
-    <t>0.8153,0.1036,0.0492,0.0099</t>
-  </si>
-  <si>
-    <t>0.9321,0.0294,0.0132,0.0111</t>
-  </si>
-  <si>
-    <t>0.8350,0.0569,0.0765,0.0320</t>
-  </si>
-  <si>
-    <t>0.9048,0.0313,0.0771,0.0033</t>
-  </si>
-  <si>
-    <t>0.7903,0.1114,0.0843,0.0247</t>
-  </si>
-  <si>
-    <t>0.9862,0.0036,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9884,0.0019,0.0001,0.0034</t>
-  </si>
-  <si>
-    <t>0.9702,0.0080,0.0018,0.0090</t>
-  </si>
-  <si>
-    <t>0.9927,0.0013,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9848,0.0023,0.0013,0.0049</t>
-  </si>
-  <si>
-    <t>0.9885,0.0012,0.0002,0.0047</t>
-  </si>
-  <si>
-    <t>0.9790,0.0007,0.0001,0.0184</t>
-  </si>
-  <si>
-    <t>0.9890,0.0007,0.0001,0.0050</t>
-  </si>
-  <si>
-    <t>0.5822,0.5397,0.0209,0.0091</t>
-  </si>
-  <si>
-    <t>0.6972,0.4175,0.0179,0.0017</t>
-  </si>
-  <si>
-    <t>0.5153,0.5992,0.0112,0.0026</t>
-  </si>
-  <si>
-    <t>0.3842,0.4828,0.2863,0.0068</t>
-  </si>
-  <si>
-    <t>0.9723,0.0218,0.0042,0.0020</t>
-  </si>
-  <si>
-    <t>0.9331,0.0198,0.0161,0.0156</t>
-  </si>
-  <si>
-    <t>0.9538,0.0251,0.0004,0.0056</t>
-  </si>
-  <si>
-    <t>0.8895,0.0697,0.0048,0.0136</t>
-  </si>
-  <si>
-    <t>0.0060,0.0805,0.9899,0.0004</t>
-  </si>
-  <si>
-    <t>0.9710,0.0221,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.0235,0.0129,0.9842,0.0004</t>
-  </si>
-  <si>
-    <t>0.0210,0.0362,0.9690,0.0025</t>
-  </si>
-  <si>
-    <t>0.0245,0.0085,0.9765,0.0014</t>
-  </si>
-  <si>
-    <t>0.0284,0.2885,0.8578,0.0011</t>
-  </si>
-  <si>
-    <t>0.1426,0.0170,0.8859,0.0053</t>
-  </si>
-  <si>
-    <t>0.0096,0.0022,0.9901,0.0025</t>
-  </si>
-  <si>
-    <t>0.0119,0.0033,0.9884,0.0006</t>
-  </si>
-  <si>
-    <t>0.4052,0.1498,0.5008,0.0603</t>
-  </si>
-  <si>
-    <t>0.2480,0.2107,0.5976,0.0052</t>
-  </si>
-  <si>
-    <t>0.6205,0.0217,0.4918,0.0169</t>
-  </si>
-  <si>
-    <t>0.3418,0.2144,0.4464,0.0060</t>
-  </si>
-  <si>
-    <t>0.2081,0.5088,0.3662,0.0036</t>
-  </si>
-  <si>
-    <t>0.3173,0.5557,0.1429,0.0063</t>
-  </si>
-  <si>
-    <t>0.7861,0.0178,0.2087,0.0203</t>
-  </si>
-  <si>
-    <t>0.5042,0.1457,0.4194,0.0070</t>
-  </si>
-  <si>
-    <t>0.8426,0.2183,0.0110,0.0013</t>
-  </si>
-  <si>
-    <t>0.5127,0.6182,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.9570,0.0667,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.9824,0.0141,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9178,0.1217,0.0071,0.0018</t>
-  </si>
-  <si>
-    <t>0.6808,0.0244,0.4106,0.0088</t>
-  </si>
-  <si>
-    <t>0.8116,0.0257,0.1459,0.0151</t>
-  </si>
-  <si>
-    <t>0.7533,0.1172,0.0720,0.0254</t>
-  </si>
-  <si>
-    <t>0.6094,0.0569,0.3648,0.0391</t>
-  </si>
-  <si>
-    <t>0.8631,0.0082,0.0347,0.0568</t>
-  </si>
-  <si>
-    <t>0.0282,0.0112,0.9205,0.0899</t>
-  </si>
-  <si>
-    <t>0.0046,0.0075,0.9676,0.0414</t>
-  </si>
-  <si>
-    <t>0.0237,0.0345,0.9634,0.0067</t>
-  </si>
-  <si>
-    <t>0.1417,0.0306,0.8178,0.0264</t>
-  </si>
-  <si>
-    <t>0.1135,0.2619,0.7485,0.0140</t>
-  </si>
-  <si>
-    <t>0.9715,0.0034,0.0002,0.0176</t>
-  </si>
-  <si>
-    <t>0.9955,0.0007,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9848,0.0046,0.0003,0.0030</t>
-  </si>
-  <si>
-    <t>0.9913,0.0013,0.0002,0.0024</t>
-  </si>
-  <si>
-    <t>0.9942,0.0013,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9889,0.0033,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9878,0.0010,0.0003,0.0067</t>
-  </si>
-  <si>
-    <t>0.9938,0.0021,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.2188,0.0090,0.9227,0.0015</t>
-  </si>
-  <si>
-    <t>0.2271,0.2333,0.5900,0.0539</t>
-  </si>
-  <si>
-    <t>0.8053,0.0080,0.0124,0.1608</t>
-  </si>
-  <si>
-    <t>0.0091,0.0088,0.9833,0.0018</t>
-  </si>
-  <si>
-    <t>0.0022,0.0022,0.9948,0.0018</t>
-  </si>
-  <si>
-    <t>0.0497,0.0445,0.9229,0.0027</t>
-  </si>
-  <si>
-    <t>0.0015,0.0025,0.9949,0.0026</t>
-  </si>
-  <si>
-    <t>0.0617,0.0708,0.8932,0.0030</t>
-  </si>
-  <si>
-    <t>0.0209,0.0116,0.9812,0.0013</t>
-  </si>
-  <si>
-    <t>0.0119,0.0123,0.9759,0.0009</t>
-  </si>
-  <si>
-    <t>0.3527,0.0643,0.5872,0.0879</t>
-  </si>
-  <si>
-    <t>0.8452,0.0046,0.2060,0.0056</t>
-  </si>
-  <si>
-    <t>0.7461,0.0029,0.3585,0.0146</t>
-  </si>
-  <si>
-    <t>0.7952,0.0183,0.2289,0.0103</t>
-  </si>
-  <si>
-    <t>0.9824,0.0164,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9910,0.0031,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9966,0.0015,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9937,0.0040,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9959,0.0005,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9928,0.0028,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9856,0.0030,0.0001,0.0025</t>
-  </si>
-  <si>
-    <t>0.9882,0.0050,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0303,0.1658,0.8235,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.0222,0.9925,0.0008</t>
-  </si>
-  <si>
-    <t>0.0032,0.2974,0.9535,0.0032</t>
-  </si>
-  <si>
-    <t>0.0841,0.0646,0.8737,0.0010</t>
-  </si>
-  <si>
-    <t>0.0050,0.0011,0.9959,0.0006</t>
-  </si>
-  <si>
-    <t>0.4411,0.0199,0.3647,0.1591</t>
-  </si>
-  <si>
-    <t>0.0746,0.0104,0.9029,0.0203</t>
-  </si>
-  <si>
-    <t>0.3054,0.0276,0.6878,0.0313</t>
-  </si>
-  <si>
-    <t>0.6210,0.0011,0.0027,0.5382</t>
-  </si>
-  <si>
-    <t>0.2471,0.0250,0.0040,0.8740</t>
-  </si>
-  <si>
-    <t>0.0463,0.0019,0.0006,0.9803</t>
-  </si>
-  <si>
-    <t>0.0031,0.0018,0.0003,0.9981</t>
-  </si>
-  <si>
-    <t>0.0029,0.0007,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.6106,0.0052,0.0038,0.5622</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.6812,0.0081,0.0049,0.4106</t>
+  </si>
+  <si>
+    <t>0.0430,0.0014,0.0003,0.9864</t>
+  </si>
+  <si>
+    <t>0.4390,0.0097,0.0040,0.7402</t>
+  </si>
+  <si>
+    <t>0.0380,0.0016,0.0010,0.9874</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9927,0.0010,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9924,0.0018,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9916,0.0033,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0011,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9888,0.0018,0.0003,0.0035</t>
+  </si>
+  <si>
+    <t>0.7044,0.0428,0.2633,0.0268</t>
+  </si>
+  <si>
+    <t>0.1992,0.0293,0.8448,0.0086</t>
+  </si>
+  <si>
+    <t>0.0986,0.0195,0.9076,0.0058</t>
+  </si>
+  <si>
+    <t>0.0418,0.0152,0.9477,0.0023</t>
+  </si>
+  <si>
+    <t>0.7840,0.0520,0.2142,0.0051</t>
+  </si>
+  <si>
+    <t>0.0579,0.9500,0.0094,0.0009</t>
+  </si>
+  <si>
+    <t>0.0967,0.9359,0.0049,0.0006</t>
+  </si>
+  <si>
+    <t>0.5028,0.6044,0.0174,0.0011</t>
+  </si>
+  <si>
+    <t>0.2031,0.8653,0.0069,0.0009</t>
+  </si>
+  <si>
+    <t>0.0431,0.9651,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.7935,0.0070,0.2765,0.0080</t>
+  </si>
+  <si>
+    <t>0.4638,0.0074,0.5146,0.0479</t>
+  </si>
+  <si>
+    <t>0.1587,0.0074,0.9041,0.0009</t>
+  </si>
+  <si>
+    <t>0.1359,0.0085,0.8435,0.0344</t>
+  </si>
+  <si>
+    <t>0.0527,0.0078,0.9574,0.0027</t>
+  </si>
+  <si>
+    <t>0.1342,0.0026,0.9238,0.0028</t>
+  </si>
+  <si>
+    <t>0.0064,0.0019,0.9777,0.0447</t>
+  </si>
+  <si>
+    <t>0.5581,0.4260,0.0686,0.0188</t>
+  </si>
+  <si>
+    <t>0.3146,0.1900,0.6129,0.0026</t>
+  </si>
+  <si>
+    <t>0.0033,0.0295,0.9828,0.0115</t>
+  </si>
+  <si>
+    <t>0.0074,0.9448,0.4461,0.0012</t>
+  </si>
+  <si>
+    <t>0.8700,0.0829,0.0336,0.0148</t>
+  </si>
+  <si>
+    <t>0.7147,0.2505,0.0732,0.0167</t>
+  </si>
+  <si>
+    <t>0.9036,0.1503,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.0755,0.9240,0.0394,0.0042</t>
+  </si>
+  <si>
+    <t>0.0576,0.6661,0.5966,0.0246</t>
+  </si>
+  <si>
+    <t>0.0781,0.0839,0.9073,0.0115</t>
+  </si>
+  <si>
+    <t>0.0640,0.1945,0.8404,0.0550</t>
+  </si>
+  <si>
+    <t>0.4869,0.0053,0.4384,0.0487</t>
+  </si>
+  <si>
+    <t>0.0273,0.5186,0.8302,0.0023</t>
+  </si>
+  <si>
+    <t>0.0070,0.9638,0.0501,0.0005</t>
+  </si>
+  <si>
+    <t>0.0098,0.0047,0.9799,0.0062</t>
+  </si>
+  <si>
+    <t>0.0149,0.4829,0.0099,0.9552</t>
+  </si>
+  <si>
+    <t>0.0070,0.9790,0.0292,0.0119</t>
+  </si>
+  <si>
+    <t>0.0014,0.9890,0.0864,0.0011</t>
+  </si>
+  <si>
+    <t>0.0023,0.9841,0.0671,0.0279</t>
+  </si>
+  <si>
+    <t>0.0036,0.0528,0.9767,0.0029</t>
+  </si>
+  <si>
+    <t>0.0076,0.0573,0.9802,0.0007</t>
+  </si>
+  <si>
+    <t>0.0970,0.0050,0.9183,0.0093</t>
+  </si>
+  <si>
+    <t>0.0275,0.0036,0.9812,0.0009</t>
+  </si>
+  <si>
+    <t>0.0132,0.0090,0.9550,0.0363</t>
+  </si>
+  <si>
+    <t>0.0531,0.0395,0.9302,0.0066</t>
+  </si>
+  <si>
+    <t>0.9904,0.0079,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9889,0.0016,0.0002,0.0039</t>
+  </si>
+  <si>
+    <t>0.9840,0.0031,0.0008,0.0045</t>
+  </si>
+  <si>
+    <t>0.0144,0.1433,0.9717,0.0005</t>
+  </si>
+  <si>
+    <t>0.9851,0.0032,0.0003,0.0041</t>
+  </si>
+  <si>
+    <t>0.9889,0.0040,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9807,0.0116,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.0037,0.8852,0.8891,0.0006</t>
+  </si>
+  <si>
+    <t>0.0800,0.1425,0.8701,0.0029</t>
+  </si>
+  <si>
+    <t>0.0129,0.1318,0.9237,0.0099</t>
+  </si>
+  <si>
+    <t>0.0009,0.9223,0.9585,0.0003</t>
+  </si>
+  <si>
+    <t>0.0612,0.0067,0.9599,0.0007</t>
+  </si>
+  <si>
+    <t>0.0376,0.8254,0.1289,0.0004</t>
+  </si>
+  <si>
+    <t>0.0267,0.9738,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.9473,0.0070,0.0497,0.0033</t>
+  </si>
+  <si>
+    <t>0.8166,0.0662,0.1460,0.0272</t>
+  </si>
+  <si>
+    <t>0.0034,0.0120,0.9941,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.8937,0.9590,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.8596,0.9404,0.0008</t>
+  </si>
+  <si>
+    <t>0.0035,0.9772,0.2072,0.0010</t>
+  </si>
+  <si>
+    <t>0.0029,0.9748,0.2953,0.0003</t>
+  </si>
+  <si>
+    <t>0.0085,0.0007,0.0032,0.9895</t>
+  </si>
+  <si>
+    <t>0.0017,0.0024,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0079,0.0049,0.0011,0.9931</t>
+  </si>
+  <si>
+    <t>0.0107,0.0024,0.0011,0.9922</t>
+  </si>
+  <si>
+    <t>0.0163,0.0034,0.0033,0.9889</t>
+  </si>
+  <si>
+    <t>0.0097,0.0004,0.0006,0.9947</t>
+  </si>
+  <si>
+    <t>0.0022,0.8865,0.9508,0.0005</t>
+  </si>
+  <si>
+    <t>0.0095,0.6217,0.9305,0.0031</t>
+  </si>
+  <si>
+    <t>0.0093,0.7409,0.8520,0.0066</t>
+  </si>
+  <si>
+    <t>0.0026,0.5355,0.9530,0.0018</t>
+  </si>
+  <si>
+    <t>0.0049,0.9247,0.5922,0.0005</t>
+  </si>
+  <si>
+    <t>0.0036,0.9569,0.3926,0.0004</t>
+  </si>
+  <si>
+    <t>0.9921,0.0026,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9774,0.0170,0.0038,0.0012</t>
+  </si>
+  <si>
+    <t>0.9868,0.0104,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9822,0.0048,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9870,0.0035,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9947,0.0003,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.9849,0.0047,0.0012,0.0032</t>
+  </si>
+  <si>
+    <t>0.9917,0.0025,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0003,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9965,0.0009,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9915,0.0002,0.0000,0.0062</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9932,0.0007,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.9924,0.0022,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9914,0.0002,0.0000,0.0043</t>
+  </si>
+  <si>
+    <t>0.9947,0.0003,0.0000,0.0023</t>
+  </si>
+  <si>
+    <t>0.0047,0.0063,0.9849,0.0116</t>
+  </si>
+  <si>
+    <t>0.1267,0.0145,0.8928,0.0109</t>
+  </si>
+  <si>
+    <t>0.8348,0.0034,0.1880,0.0098</t>
+  </si>
+  <si>
+    <t>0.1066,0.0280,0.8807,0.0068</t>
+  </si>
+  <si>
+    <t>0.2001,0.8346,0.0273,0.0031</t>
+  </si>
+  <si>
+    <t>0.0562,0.9559,0.0041,0.0015</t>
+  </si>
+  <si>
+    <t>0.0623,0.9300,0.0019,0.0062</t>
+  </si>
+  <si>
+    <t>0.7841,0.3096,0.0079,0.0030</t>
+  </si>
+  <si>
+    <t>0.1488,0.8713,0.0273,0.0030</t>
+  </si>
+  <si>
+    <t>0.0126,0.9797,0.0029,0.0020</t>
+  </si>
+  <si>
+    <t>0.8412,0.2481,0.0034,0.0034</t>
+  </si>
+  <si>
+    <t>0.6048,0.1945,0.1955,0.0224</t>
+  </si>
+  <si>
+    <t>0.3045,0.0044,0.7618,0.0225</t>
+  </si>
+  <si>
+    <t>0.7165,0.0556,0.2408,0.0083</t>
+  </si>
+  <si>
+    <t>0.6659,0.0514,0.3490,0.0282</t>
+  </si>
+  <si>
+    <t>0.3262,0.0481,0.1136,0.6414</t>
+  </si>
+  <si>
+    <t>0.0039,0.9810,0.0163,0.0207</t>
+  </si>
+  <si>
+    <t>0.0050,0.9666,0.0260,0.0406</t>
+  </si>
+  <si>
+    <t>0.3861,0.2424,0.0129,0.3306</t>
+  </si>
+  <si>
+    <t>0.0037,0.9531,0.7779,0.0014</t>
+  </si>
+  <si>
+    <t>0.1078,0.8599,0.1170,0.0010</t>
+  </si>
+  <si>
+    <t>0.9175,0.0944,0.0139,0.0023</t>
+  </si>
+  <si>
+    <t>0.9123,0.1152,0.0099,0.0009</t>
+  </si>
+  <si>
+    <t>0.9867,0.0084,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.9880,0.0034,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9815,0.0072,0.0007,0.0037</t>
+  </si>
+  <si>
+    <t>0.9765,0.0056,0.0015,0.0069</t>
+  </si>
+  <si>
+    <t>0.9844,0.0019,0.0001,0.0045</t>
+  </si>
+  <si>
+    <t>0.9761,0.0099,0.0026,0.0075</t>
+  </si>
+  <si>
+    <t>0.9720,0.0023,0.0003,0.0176</t>
+  </si>
+  <si>
+    <t>0.9844,0.0045,0.0016,0.0034</t>
+  </si>
+  <si>
+    <t>0.0017,0.8192,0.9313,0.0008</t>
+  </si>
+  <si>
+    <t>0.0112,0.2655,0.9417,0.0007</t>
+  </si>
+  <si>
+    <t>0.0241,0.1059,0.9159,0.0025</t>
+  </si>
+  <si>
+    <t>0.0629,0.0573,0.8524,0.0272</t>
+  </si>
+  <si>
+    <t>0.7608,0.0084,0.1801,0.0492</t>
+  </si>
+  <si>
+    <t>0.7853,0.0231,0.2559,0.0087</t>
+  </si>
+  <si>
+    <t>0.5695,0.0031,0.5988,0.0099</t>
+  </si>
+  <si>
+    <t>0.5153,0.1830,0.3192,0.0058</t>
+  </si>
+  <si>
+    <t>0.0868,0.0024,0.0032,0.9537</t>
+  </si>
+  <si>
+    <t>0.0010,0.0064,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0042,0.0058,0.0042,0.9931</t>
+  </si>
+  <si>
+    <t>0.0204,0.0004,0.0011,0.9908</t>
+  </si>
+  <si>
+    <t>0.0062,0.9302,0.5383,0.0040</t>
+  </si>
+  <si>
+    <t>0.9783,0.0083,0.0003,0.0046</t>
+  </si>
+  <si>
+    <t>0.4334,0.6387,0.0157,0.0027</t>
+  </si>
+  <si>
+    <t>0.9641,0.0087,0.0010,0.0157</t>
+  </si>
+  <si>
+    <t>0.8355,0.2291,0.0085,0.0014</t>
+  </si>
+  <si>
+    <t>0.9362,0.0036,0.0050,0.0401</t>
+  </si>
+  <si>
+    <t>0.2182,0.0050,0.0249,0.8397</t>
+  </si>
+  <si>
+    <t>0.9722,0.0158,0.0045,0.0022</t>
+  </si>
+  <si>
+    <t>0.0493,0.1113,0.9049,0.0120</t>
+  </si>
+  <si>
+    <t>0.8482,0.0004,0.0050,0.1384</t>
+  </si>
+  <si>
+    <t>0.9580,0.0047,0.0017,0.0284</t>
+  </si>
+  <si>
+    <t>0.7254,0.1756,0.1397,0.0179</t>
+  </si>
+  <si>
+    <t>0.8713,0.0726,0.0386,0.0167</t>
+  </si>
+  <si>
+    <t>0.8621,0.0514,0.1011,0.0055</t>
+  </si>
+  <si>
+    <t>0.7643,0.1878,0.0370,0.0056</t>
+  </si>
+  <si>
+    <t>0.6151,0.3354,0.0935,0.0079</t>
+  </si>
+  <si>
+    <t>0.8281,0.0949,0.0180,0.0175</t>
+  </si>
+  <si>
+    <t>0.9838,0.0031,0.0003,0.0060</t>
+  </si>
+  <si>
+    <t>0.9740,0.0011,0.0000,0.0176</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9885,0.0020,0.0003,0.0037</t>
+  </si>
+  <si>
+    <t>0.9884,0.0001,0.0000,0.0149</t>
+  </si>
+  <si>
+    <t>0.9927,0.0012,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9889,0.0005,0.0002,0.0062</t>
+  </si>
+  <si>
+    <t>0.9908,0.0012,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.7975,0.2813,0.0084,0.0016</t>
+  </si>
+  <si>
+    <t>0.6122,0.4867,0.0201,0.0023</t>
+  </si>
+  <si>
+    <t>0.8332,0.1995,0.0138,0.0009</t>
+  </si>
+  <si>
+    <t>0.7420,0.2163,0.1205,0.0086</t>
+  </si>
+  <si>
+    <t>0.9810,0.0062,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9339,0.0514,0.0108,0.0046</t>
+  </si>
+  <si>
+    <t>0.9649,0.0078,0.0002,0.0088</t>
+  </si>
+  <si>
+    <t>0.9579,0.0100,0.0026,0.0158</t>
+  </si>
+  <si>
+    <t>0.0119,0.0091,0.9884,0.0011</t>
+  </si>
+  <si>
+    <t>0.9812,0.0096,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.0050,0.0078,0.9849,0.0081</t>
+  </si>
+  <si>
+    <t>0.0129,0.0200,0.9823,0.0010</t>
+  </si>
+  <si>
+    <t>0.0920,0.0150,0.9023,0.0122</t>
+  </si>
+  <si>
+    <t>0.0375,0.0492,0.9114,0.0055</t>
+  </si>
+  <si>
+    <t>0.0249,0.0185,0.9688,0.0005</t>
+  </si>
+  <si>
+    <t>0.0166,0.0037,0.9839,0.0015</t>
+  </si>
+  <si>
+    <t>0.0027,0.0025,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.1581,0.0274,0.8336,0.0091</t>
+  </si>
+  <si>
+    <t>0.1630,0.0114,0.9092,0.0027</t>
+  </si>
+  <si>
+    <t>0.7752,0.0348,0.2115,0.0114</t>
+  </si>
+  <si>
+    <t>0.5645,0.0505,0.5077,0.0058</t>
+  </si>
+  <si>
+    <t>0.0535,0.8669,0.1065,0.0005</t>
+  </si>
+  <si>
+    <t>0.6639,0.0732,0.2496,0.0035</t>
+  </si>
+  <si>
+    <t>0.7061,0.0478,0.2998,0.0265</t>
+  </si>
+  <si>
+    <t>0.2999,0.2003,0.5364,0.0047</t>
+  </si>
+  <si>
+    <t>0.8888,0.1254,0.0062,0.0084</t>
+  </si>
+  <si>
+    <t>0.9481,0.0786,0.0050,0.0006</t>
+  </si>
+  <si>
+    <t>0.3635,0.7097,0.0226,0.0047</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9853,0.0077,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.4769,0.0333,0.6007,0.0144</t>
+  </si>
+  <si>
+    <t>0.8545,0.0090,0.2322,0.0027</t>
+  </si>
+  <si>
+    <t>0.7302,0.0228,0.1049,0.1315</t>
+  </si>
+  <si>
+    <t>0.5050,0.0205,0.5564,0.0154</t>
+  </si>
+  <si>
+    <t>0.9020,0.0050,0.0837,0.0107</t>
+  </si>
+  <si>
+    <t>0.0137,0.0088,0.9631,0.0105</t>
+  </si>
+  <si>
+    <t>0.1143,0.1105,0.7952,0.0281</t>
+  </si>
+  <si>
+    <t>0.0893,0.0544,0.8945,0.0167</t>
+  </si>
+  <si>
+    <t>0.1023,0.0045,0.5815,0.2453</t>
+  </si>
+  <si>
+    <t>0.1865,0.0277,0.8661,0.0027</t>
+  </si>
+  <si>
+    <t>0.9899,0.0005,0.0000,0.0049</t>
+  </si>
+  <si>
+    <t>0.9927,0.0017,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9852,0.0013,0.0002,0.0076</t>
+  </si>
+  <si>
+    <t>0.9928,0.0038,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9909,0.0016,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9875,0.0033,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9878,0.0037,0.0005,0.0025</t>
+  </si>
+  <si>
+    <t>0.9907,0.0013,0.0002,0.0035</t>
+  </si>
+  <si>
+    <t>0.0792,0.0469,0.9475,0.0014</t>
+  </si>
+  <si>
+    <t>0.4284,0.2665,0.4640,0.0144</t>
+  </si>
+  <si>
+    <t>0.9292,0.0158,0.0296,0.0181</t>
+  </si>
+  <si>
+    <t>0.0150,0.0093,0.9819,0.0006</t>
+  </si>
+  <si>
+    <t>0.0020,0.0043,0.9914,0.0056</t>
+  </si>
+  <si>
+    <t>0.0383,0.0638,0.9224,0.0015</t>
+  </si>
+  <si>
+    <t>0.0021,0.0013,0.9945,0.0026</t>
+  </si>
+  <si>
+    <t>0.0653,0.0291,0.8904,0.0142</t>
+  </si>
+  <si>
+    <t>0.0266,0.0193,0.9774,0.0016</t>
+  </si>
+  <si>
+    <t>0.0083,0.0104,0.9730,0.0023</t>
+  </si>
+  <si>
+    <t>0.1847,0.0179,0.8204,0.0232</t>
+  </si>
+  <si>
+    <t>0.8381,0.0025,0.2946,0.0036</t>
+  </si>
+  <si>
+    <t>0.6929,0.0056,0.4935,0.0105</t>
+  </si>
+  <si>
+    <t>0.8616,0.0079,0.1636,0.0087</t>
+  </si>
+  <si>
+    <t>0.9772,0.0023,0.0000,0.0037</t>
+  </si>
+  <si>
+    <t>0.9943,0.0018,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9916,0.0032,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9902,0.0070,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9896,0.0023,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9847,0.0168,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9895,0.0015,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9850,0.0022,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.1109,0.0831,0.7793,0.0056</t>
+  </si>
+  <si>
+    <t>0.0066,0.0383,0.9710,0.0011</t>
+  </si>
+  <si>
+    <t>0.0282,0.1286,0.8815,0.0236</t>
+  </si>
+  <si>
+    <t>0.1473,0.0278,0.8535,0.0026</t>
+  </si>
+  <si>
+    <t>0.0164,0.0025,0.9593,0.0414</t>
+  </si>
+  <si>
+    <t>0.1121,0.0105,0.9113,0.0068</t>
+  </si>
+  <si>
+    <t>0.1033,0.0183,0.8520,0.0590</t>
+  </si>
+  <si>
+    <t>0.0140,0.0017,0.8591,0.2426</t>
+  </si>
+  <si>
+    <t>0.6142,0.0015,0.0020,0.5790</t>
+  </si>
+  <si>
+    <t>0.0438,0.0092,0.0091,0.9733</t>
+  </si>
+  <si>
+    <t>0.0762,0.0109,0.0080,0.9563</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0009,0.0009,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.2909,0.0129,0.0273,0.7794</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
